--- a/output/graficos_envejecimiento/plot_comunal_d_enveje_a_2024_los_rios.xlsx
+++ b/output/graficos_envejecimiento/plot_comunal_d_enveje_a_2024_los_rios.xlsx
@@ -391,10 +391,10 @@
         <v>139.156913820303</v>
       </c>
       <c r="C2">
-        <v>15.35276954792777</v>
+        <v>15.35276954792776</v>
       </c>
       <c r="D2">
-        <v>63.28279016323266</v>
+        <v>63.28279016323265</v>
       </c>
       <c r="E2">
         <v>21.36444028883957</v>
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>139.7836538461538</v>
+        <v>139.7836538461539</v>
       </c>
       <c r="C4">
         <v>16.55556661028753</v>
@@ -486,13 +486,13 @@
         <v>112.280701754386</v>
       </c>
       <c r="C7">
-        <v>18.30905127910978</v>
+        <v>18.30905127910979</v>
       </c>
       <c r="D7">
         <v>61.13341746013537</v>
       </c>
       <c r="E7">
-        <v>20.55753126075485</v>
+        <v>20.55753126075484</v>
       </c>
     </row>
     <row r="8">
@@ -527,7 +527,7 @@
         <v>17.17921774664332</v>
       </c>
       <c r="D9">
-        <v>61.04845300642148</v>
+        <v>61.04845300642149</v>
       </c>
       <c r="E9">
         <v>21.7723292469352</v>
@@ -546,10 +546,10 @@
         <v>16.13152351977533</v>
       </c>
       <c r="D10">
-        <v>60.19190264451206</v>
+        <v>60.19190264451205</v>
       </c>
       <c r="E10">
-        <v>23.67657383571261</v>
+        <v>23.67657383571262</v>
       </c>
     </row>
     <row r="11">
@@ -565,10 +565,10 @@
         <v>18.23663624511082</v>
       </c>
       <c r="D11">
-        <v>60.51173402868318</v>
+        <v>60.51173402868317</v>
       </c>
       <c r="E11">
-        <v>21.251629726206</v>
+        <v>21.25162972620599</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         <v>16.2865935453326</v>
       </c>
       <c r="D12">
-        <v>60.10415844709225</v>
+        <v>60.10415844709224</v>
       </c>
       <c r="E12">
         <v>23.60924800757516</v>
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>66.59412404787813</v>
+        <v>66.59412404787814</v>
       </c>
       <c r="C13">
         <v>21.77037271004422</v>
@@ -606,7 +606,7 @@
         <v>63.73183828174353</v>
       </c>
       <c r="E13">
-        <v>14.49778900821225</v>
+        <v>14.49778900821226</v>
       </c>
     </row>
   </sheetData>
